--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_IRUKI TAKE.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_IRUKI TAKE.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>J. URTXULUTEGI NAVARRI</t>
+          <t>U. PEREZ SANZ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -562,76 +562,76 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D2" t="n">
-        <v>50.6492</v>
+        <v>45.3959</v>
       </c>
       <c r="E2" t="n">
-        <v>49.9456</v>
+        <v>35.8626</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7039</v>
+        <v>9.533300000000001</v>
       </c>
       <c r="G2" t="n">
-        <v>20.8937</v>
+        <v>21.1797</v>
       </c>
       <c r="H2" t="n">
-        <v>17.4566</v>
+        <v>5.033199999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>3.437</v>
+        <v>16.1465</v>
       </c>
       <c r="J2" t="n">
-        <v>47.4599</v>
+        <v>56.0001</v>
       </c>
       <c r="K2" t="n">
-        <v>30.9624</v>
+        <v>27.1602</v>
       </c>
       <c r="L2" t="n">
-        <v>16.498</v>
+        <v>28.84</v>
       </c>
       <c r="M2" t="n">
-        <v>-26.5664</v>
+        <v>-34.8204</v>
       </c>
       <c r="N2" t="n">
-        <v>-13.506</v>
+        <v>-22.1269</v>
       </c>
       <c r="O2" t="n">
-        <v>-13.0602</v>
+        <v>-12.6934</v>
       </c>
       <c r="P2" t="n">
-        <v>12.5456</v>
+        <v>15.2478</v>
       </c>
       <c r="Q2" t="n">
-        <v>-26.2488</v>
+        <v>-38.6015</v>
       </c>
       <c r="R2" t="n">
-        <v>38.795</v>
+        <v>53.8494</v>
       </c>
       <c r="S2" t="n">
-        <v>18.8111</v>
+        <v>-2.2148</v>
       </c>
       <c r="T2" t="n">
-        <v>16.1368</v>
+        <v>-3.4281</v>
       </c>
       <c r="U2" t="n">
-        <v>2.6746</v>
+        <v>1.2134</v>
       </c>
       <c r="V2" t="n">
-        <v>-1.6006</v>
+        <v>11.1828</v>
       </c>
       <c r="W2" t="n">
-        <v>12.5983</v>
+        <v>21.8923</v>
       </c>
       <c r="X2" t="n">
-        <v>-14.1989</v>
+        <v>-10.7095</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>U. PEREZ SANZ</t>
+          <t>J. URTXULUTEGI NAVARRI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,70 +640,70 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D3" t="n">
-        <v>36.4993</v>
+        <v>38.5976</v>
       </c>
       <c r="E3" t="n">
-        <v>29.0777</v>
+        <v>37.7632</v>
       </c>
       <c r="F3" t="n">
-        <v>7.4213</v>
+        <v>0.8346000000000009</v>
       </c>
       <c r="G3" t="n">
-        <v>21.1797</v>
+        <v>20.8937</v>
       </c>
       <c r="H3" t="n">
-        <v>5.033199999999999</v>
+        <v>17.4566</v>
       </c>
       <c r="I3" t="n">
-        <v>16.1465</v>
+        <v>3.437</v>
       </c>
       <c r="J3" t="n">
-        <v>56.0001</v>
+        <v>47.4599</v>
       </c>
       <c r="K3" t="n">
-        <v>27.1602</v>
+        <v>30.9624</v>
       </c>
       <c r="L3" t="n">
-        <v>28.84</v>
+        <v>16.498</v>
       </c>
       <c r="M3" t="n">
-        <v>-34.8204</v>
+        <v>-26.5664</v>
       </c>
       <c r="N3" t="n">
-        <v>-22.1269</v>
+        <v>-13.506</v>
       </c>
       <c r="O3" t="n">
-        <v>-12.6934</v>
+        <v>-13.0602</v>
       </c>
       <c r="P3" t="n">
-        <v>15.2478</v>
+        <v>12.5456</v>
       </c>
       <c r="Q3" t="n">
-        <v>-38.6015</v>
+        <v>-26.2488</v>
       </c>
       <c r="R3" t="n">
-        <v>53.8494</v>
+        <v>38.795</v>
       </c>
       <c r="S3" t="n">
-        <v>-11.1111</v>
+        <v>6.7591</v>
       </c>
       <c r="T3" t="n">
-        <v>-10.213</v>
+        <v>3.9543</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.8983000000000003</v>
+        <v>2.8053</v>
       </c>
       <c r="V3" t="n">
-        <v>11.1828</v>
+        <v>-1.6006</v>
       </c>
       <c r="W3" t="n">
-        <v>21.8923</v>
+        <v>12.5983</v>
       </c>
       <c r="X3" t="n">
-        <v>-10.7095</v>
+        <v>-14.1989</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>19</v>
       </c>
       <c r="D4" t="n">
-        <v>11.6534</v>
+        <v>18.7874</v>
       </c>
       <c r="E4" t="n">
-        <v>21.6086</v>
+        <v>27.1103</v>
       </c>
       <c r="F4" t="n">
-        <v>-9.9549</v>
+        <v>-8.322900000000001</v>
       </c>
       <c r="G4" t="n">
         <v>16.142</v>
@@ -766,13 +766,13 @@
         <v>34.7416</v>
       </c>
       <c r="S4" t="n">
-        <v>-8.701099999999999</v>
+        <v>-1.5676</v>
       </c>
       <c r="T4" t="n">
-        <v>-6.9413</v>
+        <v>-1.4393</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.7601</v>
+        <v>-0.1280000000000002</v>
       </c>
       <c r="V4" t="n">
         <v>5.5642</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>B. ETXEBERRIA AGUIRREZABALA</t>
+          <t>E. HUIZI ZUBELDIA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D5" t="n">
-        <v>11.0248</v>
+        <v>5.2098</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.0517</v>
+        <v>7.207700000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>13.0763</v>
+        <v>-1.9981</v>
       </c>
       <c r="G5" t="n">
-        <v>-21.2013</v>
+        <v>-16.7509</v>
       </c>
       <c r="H5" t="n">
-        <v>-17.1612</v>
+        <v>-2.536700000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>-4.0399</v>
+        <v>-14.2141</v>
       </c>
       <c r="J5" t="n">
-        <v>18.79</v>
+        <v>29.0888</v>
       </c>
       <c r="K5" t="n">
-        <v>5.633999999999999</v>
+        <v>19.9316</v>
       </c>
       <c r="L5" t="n">
-        <v>13.1565</v>
+        <v>9.1572</v>
       </c>
       <c r="M5" t="n">
-        <v>-39.9911</v>
+        <v>-45.8396</v>
       </c>
       <c r="N5" t="n">
-        <v>-22.7951</v>
+        <v>-22.4681</v>
       </c>
       <c r="O5" t="n">
-        <v>-17.1961</v>
+        <v>-23.3717</v>
       </c>
       <c r="P5" t="n">
-        <v>1.544199999999999</v>
+        <v>24.1258</v>
       </c>
       <c r="Q5" t="n">
-        <v>-55.3932</v>
+        <v>-38.9875</v>
       </c>
       <c r="R5" t="n">
-        <v>56.9375</v>
+        <v>63.1135</v>
       </c>
       <c r="S5" t="n">
-        <v>42.9736</v>
+        <v>4.7059</v>
       </c>
       <c r="T5" t="n">
-        <v>22.3862</v>
+        <v>-2.5733</v>
       </c>
       <c r="U5" t="n">
-        <v>20.5875</v>
+        <v>7.2794</v>
       </c>
       <c r="V5" t="n">
-        <v>-12.2914</v>
+        <v>-6.871299999999999</v>
       </c>
       <c r="W5" t="n">
-        <v>12.1656</v>
+        <v>19.6799</v>
       </c>
       <c r="X5" t="n">
-        <v>-24.457</v>
+        <v>-26.5512</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. ALDA IRAOLA</t>
+          <t>A. ARMENDARIZ LOPEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,70 +874,70 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D6" t="n">
-        <v>2.967899999999999</v>
+        <v>0.1958000000000002</v>
       </c>
       <c r="E6" t="n">
-        <v>-6.2484</v>
+        <v>-0.8637000000000006</v>
       </c>
       <c r="F6" t="n">
-        <v>9.216100000000001</v>
+        <v>1.059399999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>-12.0985</v>
+        <v>-9.517600000000002</v>
       </c>
       <c r="H6" t="n">
-        <v>-17.6837</v>
+        <v>-5.734299999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>5.5854</v>
+        <v>-3.7832</v>
       </c>
       <c r="J6" t="n">
-        <v>10.3924</v>
+        <v>20.04</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.5465999999999993</v>
+        <v>11.1441</v>
       </c>
       <c r="L6" t="n">
-        <v>10.9392</v>
+        <v>8.895800000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>-22.4903</v>
+        <v>-29.5579</v>
       </c>
       <c r="N6" t="n">
-        <v>-17.137</v>
+        <v>-16.8783</v>
       </c>
       <c r="O6" t="n">
-        <v>-5.353199999999999</v>
+        <v>-12.679</v>
       </c>
       <c r="P6" t="n">
-        <v>10.8084</v>
+        <v>14.8614</v>
       </c>
       <c r="Q6" t="n">
-        <v>-29.3369</v>
+        <v>-26.0556</v>
       </c>
       <c r="R6" t="n">
-        <v>40.1458</v>
+        <v>40.918</v>
       </c>
       <c r="S6" t="n">
-        <v>6.466200000000001</v>
+        <v>-1.1679</v>
       </c>
       <c r="T6" t="n">
-        <v>6.894699999999999</v>
+        <v>-1.718</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4287999999999998</v>
+        <v>0.5506</v>
       </c>
       <c r="V6" t="n">
-        <v>-2.2084</v>
+        <v>-3.9803</v>
       </c>
       <c r="W6" t="n">
-        <v>5.802</v>
+        <v>6.8709</v>
       </c>
       <c r="X6" t="n">
-        <v>-8.010300000000001</v>
+        <v>-10.8512</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.0203</v>
+        <v>-0.0005</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4175</v>
+        <v>0.5177</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.4379</v>
+        <v>-0.5182</v>
       </c>
       <c r="G7" t="n">
         <v>-0.1859</v>
@@ -1000,13 +1000,13 @@
         <v>0.579</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1276</v>
+        <v>-0.1077</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.238</v>
+        <v>-0.1378</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1104</v>
+        <v>0.0301</v>
       </c>
       <c r="V7" t="n">
         <v>-0.2859</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>E. HUIZI ZUBELDIA</t>
+          <t>A. ALDA IRAOLA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>25</v>
       </c>
       <c r="D8" t="n">
-        <v>-4.6242</v>
+        <v>-0.02290000000000036</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.255999999999998</v>
+        <v>-11.0582</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.3682</v>
+        <v>11.0352</v>
       </c>
       <c r="G8" t="n">
-        <v>-16.7509</v>
+        <v>-12.0985</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.536700000000001</v>
+        <v>-17.6837</v>
       </c>
       <c r="I8" t="n">
-        <v>-14.2141</v>
+        <v>5.5854</v>
       </c>
       <c r="J8" t="n">
-        <v>29.0888</v>
+        <v>10.3924</v>
       </c>
       <c r="K8" t="n">
-        <v>19.9316</v>
+        <v>-0.5465999999999993</v>
       </c>
       <c r="L8" t="n">
-        <v>9.1572</v>
+        <v>10.9392</v>
       </c>
       <c r="M8" t="n">
-        <v>-45.8396</v>
+        <v>-22.4903</v>
       </c>
       <c r="N8" t="n">
-        <v>-22.4681</v>
+        <v>-17.137</v>
       </c>
       <c r="O8" t="n">
-        <v>-23.3717</v>
+        <v>-5.353199999999999</v>
       </c>
       <c r="P8" t="n">
-        <v>24.1258</v>
+        <v>10.8084</v>
       </c>
       <c r="Q8" t="n">
-        <v>-38.9875</v>
+        <v>-29.3369</v>
       </c>
       <c r="R8" t="n">
-        <v>63.1135</v>
+        <v>40.1458</v>
       </c>
       <c r="S8" t="n">
-        <v>-5.1279</v>
+        <v>3.4752</v>
       </c>
       <c r="T8" t="n">
-        <v>-12.0371</v>
+        <v>2.0849</v>
       </c>
       <c r="U8" t="n">
-        <v>6.9093</v>
+        <v>1.3902</v>
       </c>
       <c r="V8" t="n">
-        <v>-6.871299999999999</v>
+        <v>-2.2084</v>
       </c>
       <c r="W8" t="n">
-        <v>19.6799</v>
+        <v>5.802</v>
       </c>
       <c r="X8" t="n">
-        <v>-26.5512</v>
+        <v>-8.010300000000001</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. ARMENDARIZ LOPEZ</t>
+          <t>J. ELOSEGUI OLANO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D9" t="n">
-        <v>-7.674</v>
+        <v>-8.957700000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>-6.246499999999999</v>
+        <v>-1.043399999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.4274</v>
+        <v>-7.9141</v>
       </c>
       <c r="G9" t="n">
-        <v>-9.517600000000002</v>
+        <v>-8.059999999999999</v>
       </c>
       <c r="H9" t="n">
-        <v>-5.734299999999999</v>
+        <v>-5.6464</v>
       </c>
       <c r="I9" t="n">
-        <v>-3.7832</v>
+        <v>-2.413499999999999</v>
       </c>
       <c r="J9" t="n">
-        <v>20.04</v>
+        <v>5.8629</v>
       </c>
       <c r="K9" t="n">
-        <v>11.1441</v>
+        <v>1.7742</v>
       </c>
       <c r="L9" t="n">
-        <v>8.895800000000001</v>
+        <v>4.089</v>
       </c>
       <c r="M9" t="n">
-        <v>-29.5579</v>
+        <v>-13.9224</v>
       </c>
       <c r="N9" t="n">
-        <v>-16.8783</v>
+        <v>-7.4205</v>
       </c>
       <c r="O9" t="n">
-        <v>-12.679</v>
+        <v>-6.5021</v>
       </c>
       <c r="P9" t="n">
-        <v>14.8614</v>
+        <v>10.0362</v>
       </c>
       <c r="Q9" t="n">
-        <v>-26.0556</v>
+        <v>-8.1061</v>
       </c>
       <c r="R9" t="n">
-        <v>40.918</v>
+        <v>18.1424</v>
       </c>
       <c r="S9" t="n">
-        <v>-9.037700000000001</v>
+        <v>1.1343</v>
       </c>
       <c r="T9" t="n">
-        <v>-7.101000000000001</v>
+        <v>-0.3134999999999998</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.9364</v>
+        <v>1.4478</v>
       </c>
       <c r="V9" t="n">
-        <v>-3.9803</v>
+        <v>-12.0683</v>
       </c>
       <c r="W9" t="n">
-        <v>6.8709</v>
+        <v>1.5139</v>
       </c>
       <c r="X9" t="n">
-        <v>-10.8512</v>
+        <v>-13.5821</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>O. FERNANDEZ GOENAGA</t>
+          <t>E. ERRASTI URANGA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="D10" t="n">
-        <v>-12.3693</v>
+        <v>-10.5308</v>
       </c>
       <c r="E10" t="n">
-        <v>-9.6593</v>
+        <v>-8.825799999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.7101</v>
+        <v>-1.7051</v>
       </c>
       <c r="G10" t="n">
-        <v>-5.5442</v>
+        <v>-21.9891</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.6158</v>
+        <v>-13.4665</v>
       </c>
       <c r="I10" t="n">
-        <v>-3.9286</v>
+        <v>-8.522400000000001</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.1399</v>
+        <v>6.718300000000001</v>
       </c>
       <c r="K10" t="n">
-        <v>0.3412</v>
+        <v>1.9957</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.4812000000000001</v>
+        <v>4.7231</v>
       </c>
       <c r="M10" t="n">
-        <v>-5.4043</v>
+        <v>-28.7075</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.957</v>
+        <v>-15.462</v>
       </c>
       <c r="O10" t="n">
-        <v>-3.4474</v>
+        <v>-13.2452</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.1581</v>
+        <v>20.2659</v>
       </c>
       <c r="Q10" t="n">
-        <v>-8.6853</v>
+        <v>-21.4236</v>
       </c>
       <c r="R10" t="n">
-        <v>7.5272</v>
+        <v>41.6899</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.6822</v>
+        <v>0.6836</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.1198</v>
+        <v>0.1946999999999999</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5626</v>
+        <v>0.4891999999999999</v>
       </c>
       <c r="V10" t="n">
-        <v>-3.9847</v>
+        <v>-9.491</v>
       </c>
       <c r="W10" t="n">
-        <v>0.2859</v>
+        <v>5.6852</v>
       </c>
       <c r="X10" t="n">
-        <v>-4.2705</v>
+        <v>-15.1762</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>E. ERRASTI URANGA</t>
+          <t>B. ETXEBERRIA AGUIRREZABALA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>26</v>
       </c>
       <c r="D11" t="n">
-        <v>-12.4535</v>
+        <v>-11.7565</v>
       </c>
       <c r="E11" t="n">
-        <v>-8.822899999999999</v>
+        <v>-17.2006</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.6305</v>
+        <v>5.444000000000001</v>
       </c>
       <c r="G11" t="n">
-        <v>-21.9891</v>
+        <v>-21.2013</v>
       </c>
       <c r="H11" t="n">
-        <v>-13.4665</v>
+        <v>-17.1612</v>
       </c>
       <c r="I11" t="n">
-        <v>-8.522400000000001</v>
+        <v>-4.0399</v>
       </c>
       <c r="J11" t="n">
-        <v>6.718300000000001</v>
+        <v>18.79</v>
       </c>
       <c r="K11" t="n">
-        <v>1.9957</v>
+        <v>5.633999999999999</v>
       </c>
       <c r="L11" t="n">
-        <v>4.7231</v>
+        <v>13.1565</v>
       </c>
       <c r="M11" t="n">
-        <v>-28.7075</v>
+        <v>-39.9911</v>
       </c>
       <c r="N11" t="n">
-        <v>-15.462</v>
+        <v>-22.7951</v>
       </c>
       <c r="O11" t="n">
-        <v>-13.2452</v>
+        <v>-17.1961</v>
       </c>
       <c r="P11" t="n">
-        <v>20.2659</v>
+        <v>1.544199999999999</v>
       </c>
       <c r="Q11" t="n">
-        <v>-21.4236</v>
+        <v>-55.3932</v>
       </c>
       <c r="R11" t="n">
-        <v>41.6899</v>
+        <v>56.9375</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.2392</v>
+        <v>20.1924</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1978</v>
+        <v>7.2373</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.4367</v>
+        <v>12.9552</v>
       </c>
       <c r="V11" t="n">
-        <v>-9.491</v>
+        <v>-12.2914</v>
       </c>
       <c r="W11" t="n">
-        <v>5.6852</v>
+        <v>12.1656</v>
       </c>
       <c r="X11" t="n">
-        <v>-15.1762</v>
+        <v>-24.457</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. ELOSEGUI OLANO</t>
+          <t>O. FERNANDEZ GOENAGA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="D12" t="n">
-        <v>-13.8502</v>
+        <v>-11.8619</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.626599999999999</v>
+        <v>-9.258599999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>-9.223700000000001</v>
+        <v>-2.6033</v>
       </c>
       <c r="G12" t="n">
-        <v>-8.059999999999999</v>
+        <v>-5.5442</v>
       </c>
       <c r="H12" t="n">
-        <v>-5.6464</v>
+        <v>-1.6158</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.413499999999999</v>
+        <v>-3.9286</v>
       </c>
       <c r="J12" t="n">
-        <v>5.8629</v>
+        <v>-0.1399</v>
       </c>
       <c r="K12" t="n">
-        <v>1.7742</v>
+        <v>0.3412</v>
       </c>
       <c r="L12" t="n">
-        <v>4.089</v>
+        <v>-0.4812000000000001</v>
       </c>
       <c r="M12" t="n">
-        <v>-13.9224</v>
+        <v>-5.4043</v>
       </c>
       <c r="N12" t="n">
-        <v>-7.4205</v>
+        <v>-1.957</v>
       </c>
       <c r="O12" t="n">
-        <v>-6.5021</v>
+        <v>-3.4474</v>
       </c>
       <c r="P12" t="n">
-        <v>10.0362</v>
+        <v>-1.1581</v>
       </c>
       <c r="Q12" t="n">
-        <v>-8.1061</v>
+        <v>-8.6853</v>
       </c>
       <c r="R12" t="n">
-        <v>18.1424</v>
+        <v>7.5272</v>
       </c>
       <c r="S12" t="n">
-        <v>-3.7584</v>
+        <v>-1.175</v>
       </c>
       <c r="T12" t="n">
-        <v>-3.8971</v>
+        <v>-0.7189</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1385000000000001</v>
+        <v>-0.4556000000000001</v>
       </c>
       <c r="V12" t="n">
-        <v>-12.0683</v>
+        <v>-3.9847</v>
       </c>
       <c r="W12" t="n">
-        <v>1.5139</v>
+        <v>0.2859</v>
       </c>
       <c r="X12" t="n">
-        <v>-13.5821</v>
+        <v>-4.2705</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A. IRASTORZA EZKIAGA</t>
+          <t>U. CONDE LAKUNTZA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D13" t="n">
-        <v>-18.8329</v>
+        <v>-16.215</v>
       </c>
       <c r="E13" t="n">
-        <v>-10.7674</v>
+        <v>-16.0879</v>
       </c>
       <c r="F13" t="n">
-        <v>-8.0655</v>
+        <v>-0.1274999999999999</v>
       </c>
       <c r="G13" t="n">
-        <v>-9.792400000000001</v>
+        <v>-19.2157</v>
       </c>
       <c r="H13" t="n">
-        <v>-8.177999999999999</v>
+        <v>-14.2558</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.6147</v>
+        <v>-4.959900000000001</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.5194999999999996</v>
+        <v>5.490399999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.5848</v>
+        <v>0.6657000000000002</v>
       </c>
       <c r="L13" t="n">
-        <v>1.0655</v>
+        <v>4.8251</v>
       </c>
       <c r="M13" t="n">
-        <v>-9.272500000000001</v>
+        <v>-24.7062</v>
       </c>
       <c r="N13" t="n">
-        <v>-6.5925</v>
+        <v>-14.921</v>
       </c>
       <c r="O13" t="n">
-        <v>-2.6802</v>
+        <v>-9.785400000000001</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.3511</v>
+        <v>-2.895</v>
       </c>
       <c r="Q13" t="n">
-        <v>-18.5284</v>
+        <v>-38.0225</v>
       </c>
       <c r="R13" t="n">
-        <v>17.1774</v>
+        <v>35.1274</v>
       </c>
       <c r="S13" t="n">
-        <v>-3.5606</v>
+        <v>0.1372999999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>0.05559999999999998</v>
+        <v>-1.2343</v>
       </c>
       <c r="U13" t="n">
-        <v>-3.6165</v>
+        <v>1.3719</v>
       </c>
       <c r="V13" t="n">
-        <v>-4.129</v>
+        <v>5.7584</v>
       </c>
       <c r="W13" t="n">
-        <v>8.2255</v>
+        <v>17.6789</v>
       </c>
       <c r="X13" t="n">
-        <v>-12.3546</v>
+        <v>-11.9206</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>U. CONDE LAKUNTZA</t>
+          <t>A. IRASTORZA EZKIAGA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,70 +1498,70 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D14" t="n">
-        <v>-26.6796</v>
+        <v>-16.5151</v>
       </c>
       <c r="E14" t="n">
-        <v>-21.5487</v>
+        <v>-9.9474</v>
       </c>
       <c r="F14" t="n">
-        <v>-5.130800000000001</v>
+        <v>-6.5674</v>
       </c>
       <c r="G14" t="n">
-        <v>-19.2157</v>
+        <v>-9.792400000000001</v>
       </c>
       <c r="H14" t="n">
-        <v>-14.2558</v>
+        <v>-8.177999999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>-4.959900000000001</v>
+        <v>-1.6147</v>
       </c>
       <c r="J14" t="n">
-        <v>5.490399999999999</v>
+        <v>-0.5194999999999996</v>
       </c>
       <c r="K14" t="n">
-        <v>0.6657000000000002</v>
+        <v>-1.5848</v>
       </c>
       <c r="L14" t="n">
-        <v>4.8251</v>
+        <v>1.0655</v>
       </c>
       <c r="M14" t="n">
-        <v>-24.7062</v>
+        <v>-9.272500000000001</v>
       </c>
       <c r="N14" t="n">
-        <v>-14.921</v>
+        <v>-6.5925</v>
       </c>
       <c r="O14" t="n">
-        <v>-9.785400000000001</v>
+        <v>-2.6802</v>
       </c>
       <c r="P14" t="n">
-        <v>-2.895</v>
+        <v>-1.3511</v>
       </c>
       <c r="Q14" t="n">
-        <v>-38.0225</v>
+        <v>-18.5284</v>
       </c>
       <c r="R14" t="n">
-        <v>35.1274</v>
+        <v>17.1774</v>
       </c>
       <c r="S14" t="n">
-        <v>-10.327</v>
+        <v>-1.2426</v>
       </c>
       <c r="T14" t="n">
-        <v>-6.6952</v>
+        <v>0.8758999999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>-3.6317</v>
+        <v>-2.1186</v>
       </c>
       <c r="V14" t="n">
-        <v>5.7584</v>
+        <v>-4.129</v>
       </c>
       <c r="W14" t="n">
-        <v>17.6789</v>
+        <v>8.2255</v>
       </c>
       <c r="X14" t="n">
-        <v>-11.9206</v>
+        <v>-12.3546</v>
       </c>
     </row>
     <row r="15">
@@ -1579,19 +1579,19 @@
         <v>26</v>
       </c>
       <c r="D15" t="n">
-        <v>16.29060000000001</v>
+        <v>32.32609999999998</v>
       </c>
       <c r="E15" t="n">
-        <v>28.8219</v>
+        <v>34.17589999999998</v>
       </c>
       <c r="F15" t="n">
-        <v>-12.5314</v>
+        <v>-1.8501</v>
       </c>
       <c r="G15" t="n">
         <v>-66.14019999999999</v>
       </c>
       <c r="H15" t="n">
-        <v>-48.59740000000001</v>
+        <v>-48.5974</v>
       </c>
       <c r="I15" t="n">
         <v>-17.5428</v>
@@ -1624,13 +1624,13 @@
         <v>448.7441000000001</v>
       </c>
       <c r="S15" t="n">
-        <v>13.57809999999999</v>
+        <v>29.6122</v>
       </c>
       <c r="T15" t="n">
-        <v>-2.571399999999997</v>
+        <v>2.783899999999999</v>
       </c>
       <c r="U15" t="n">
-        <v>16.1492</v>
+        <v>26.8309</v>
       </c>
       <c r="V15" t="n">
         <v>-34.4055</v>
